--- a/output/2026-09-03_02_Italia_Campania_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-03_02_Italia_Campania_Impiantistica_aspirazione_industriale.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Azienda fondata nel 1996, specializzata in impianti di aspirazione di fumo industriale. Presenza confermata su Europages; sito web proprio non individuato/verificabile.</t>
+          <t>Azienda fondata nel 1996, specializzata in impianti di aspirazione di fumo industriale. Presenza confermata su Europages; sito web proprio non individuato/verificabile. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
